--- a/data/nzd0099/nzd0099.xlsx
+++ b/data/nzd0099/nzd0099.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G313"/>
+  <dimension ref="A1:G315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8885,6 +8885,60 @@
         <v>385.4</v>
       </c>
       <c r="G313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>393.37</v>
+      </c>
+      <c r="C314" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="D314" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="E314" t="n">
+        <v>383.95</v>
+      </c>
+      <c r="F314" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>392.98</v>
+      </c>
+      <c r="C315" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="D315" t="n">
+        <v>380.05</v>
+      </c>
+      <c r="E315" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="F315" t="n">
+        <v>382.66</v>
+      </c>
+      <c r="G315" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8901,7 +8955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B331"/>
+  <dimension ref="A1:B333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12214,6 +12268,26 @@
       </c>
       <c r="B331" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>-0.98</v>
       </c>
     </row>
   </sheetData>
@@ -12382,28 +12456,28 @@
         <v>0.1268</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1419139497674132</v>
+        <v>0.137562055816077</v>
       </c>
       <c r="J2" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K2" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04866150768247601</v>
+        <v>0.04626446697097231</v>
       </c>
       <c r="M2" t="n">
-        <v>3.729083557886332</v>
+        <v>3.724920833437588</v>
       </c>
       <c r="N2" t="n">
-        <v>21.19452750174905</v>
+        <v>21.13824548443748</v>
       </c>
       <c r="O2" t="n">
-        <v>4.603751459597818</v>
+        <v>4.597634770666052</v>
       </c>
       <c r="P2" t="n">
-        <v>392.9046637242152</v>
+        <v>392.9535399260162</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12460,28 +12534,28 @@
         <v>0.1098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1222704480482315</v>
+        <v>0.1124686522258285</v>
       </c>
       <c r="J3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05211442725789928</v>
+        <v>0.04384440763885344</v>
       </c>
       <c r="M3" t="n">
-        <v>2.856244850657149</v>
+        <v>2.886536168910212</v>
       </c>
       <c r="N3" t="n">
-        <v>14.63743591303532</v>
+        <v>14.94750012514974</v>
       </c>
       <c r="O3" t="n">
-        <v>3.825890211837673</v>
+        <v>3.866199700629772</v>
       </c>
       <c r="P3" t="n">
-        <v>383.3788062958976</v>
+        <v>383.488893577559</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12538,28 +12612,28 @@
         <v>0.1394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.128554802392502</v>
+        <v>0.1229311343191221</v>
       </c>
       <c r="J4" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K4" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07223998538348464</v>
+        <v>0.06651882488130001</v>
       </c>
       <c r="M4" t="n">
-        <v>2.685946388228662</v>
+        <v>2.696853927961906</v>
       </c>
       <c r="N4" t="n">
-        <v>11.42506467452477</v>
+        <v>11.49148079121401</v>
       </c>
       <c r="O4" t="n">
-        <v>3.380098323203745</v>
+        <v>3.389908670040243</v>
       </c>
       <c r="P4" t="n">
-        <v>382.3076265372795</v>
+        <v>382.3707919471448</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12616,28 +12690,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1025510000012229</v>
+        <v>0.09894543212083236</v>
       </c>
       <c r="J5" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K5" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0476385839831629</v>
+        <v>0.04484045923553737</v>
       </c>
       <c r="M5" t="n">
-        <v>2.473199496746276</v>
+        <v>2.475784418251625</v>
       </c>
       <c r="N5" t="n">
-        <v>11.3174035700135</v>
+        <v>11.30026392698571</v>
       </c>
       <c r="O5" t="n">
-        <v>3.364134891768388</v>
+        <v>3.361586519336623</v>
       </c>
       <c r="P5" t="n">
-        <v>383.7154634986416</v>
+        <v>383.7559593794721</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12694,28 +12768,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09762239993200571</v>
+        <v>0.09540396019855711</v>
       </c>
       <c r="J6" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K6" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03969739964103958</v>
+        <v>0.03838916711343388</v>
       </c>
       <c r="M6" t="n">
-        <v>2.813172208112532</v>
+        <v>2.80671124566479</v>
       </c>
       <c r="N6" t="n">
-        <v>12.33526682721719</v>
+        <v>12.27988634405637</v>
       </c>
       <c r="O6" t="n">
-        <v>3.512159852173188</v>
+        <v>3.504266876831212</v>
       </c>
       <c r="P6" t="n">
-        <v>382.5466604194727</v>
+        <v>382.5716937062276</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12753,7 +12827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G313"/>
+  <dimension ref="A1:G315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24333,6 +24407,80 @@
         </is>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-35.71413296440125,174.5315634754584</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-35.71456398055815,174.53230168981494</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>-35.71483318769498,174.533126487119</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-35.71507875079007,174.533951354656</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-35.715255131902836,174.53480766145154</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-35.71413613769292,174.5315616201922</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-35.71457892178175,174.53229338126317</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>-35.71485215898811,174.53311708490207</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-35.71508589604978,174.5339486340711</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-35.71526756370478,174.5348039229615</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0099/nzd0099.xlsx
+++ b/data/nzd0099/nzd0099.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G315"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8941,6 +8941,33 @@
       <c r="G315" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>394.64</v>
+      </c>
+      <c r="C316" t="n">
+        <v>380.27</v>
+      </c>
+      <c r="D316" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="E316" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="F316" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B333"/>
+  <dimension ref="A1:B334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12288,6 +12315,16 @@
       </c>
       <c r="B333" t="n">
         <v>-0.98</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -12456,28 +12493,28 @@
         <v>0.1268</v>
       </c>
       <c r="I2" t="n">
-        <v>0.137562055816077</v>
+        <v>0.1363235909715539</v>
       </c>
       <c r="J2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04626446697097231</v>
+        <v>0.0457277376086368</v>
       </c>
       <c r="M2" t="n">
-        <v>3.724920833437588</v>
+        <v>3.718608531697096</v>
       </c>
       <c r="N2" t="n">
-        <v>21.13824548443748</v>
+        <v>21.08399497402202</v>
       </c>
       <c r="O2" t="n">
-        <v>4.597634770666052</v>
+        <v>4.591731152193257</v>
       </c>
       <c r="P2" t="n">
-        <v>392.9535399260162</v>
+        <v>392.9674955817874</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12534,28 +12571,28 @@
         <v>0.1098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1124686522258285</v>
+        <v>0.1086397769920092</v>
       </c>
       <c r="J3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04384440763885344</v>
+        <v>0.04096167150514485</v>
       </c>
       <c r="M3" t="n">
-        <v>2.886536168910212</v>
+        <v>2.897034110773229</v>
       </c>
       <c r="N3" t="n">
-        <v>14.94750012514974</v>
+        <v>15.02291840214038</v>
       </c>
       <c r="O3" t="n">
-        <v>3.866199700629772</v>
+        <v>3.875940969898842</v>
       </c>
       <c r="P3" t="n">
-        <v>383.488893577559</v>
+        <v>383.532039303488</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12612,28 +12649,28 @@
         <v>0.1394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1229311343191221</v>
+        <v>0.1206250491867725</v>
       </c>
       <c r="J4" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K4" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06651882488130001</v>
+        <v>0.06436060792240239</v>
       </c>
       <c r="M4" t="n">
-        <v>2.696853927961906</v>
+        <v>2.699660711899007</v>
       </c>
       <c r="N4" t="n">
-        <v>11.49148079121401</v>
+        <v>11.49957131537525</v>
       </c>
       <c r="O4" t="n">
-        <v>3.389908670040243</v>
+        <v>3.391101784873944</v>
       </c>
       <c r="P4" t="n">
-        <v>382.3707919471448</v>
+        <v>382.3967780947764</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12690,28 +12727,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09894543212083236</v>
+        <v>0.09769727761825833</v>
       </c>
       <c r="J5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04484045923553737</v>
+        <v>0.04398814896816106</v>
       </c>
       <c r="M5" t="n">
-        <v>2.475784418251625</v>
+        <v>2.47432577451698</v>
       </c>
       <c r="N5" t="n">
-        <v>11.30026392698571</v>
+        <v>11.27744704459503</v>
       </c>
       <c r="O5" t="n">
-        <v>3.361586519336623</v>
+        <v>3.358191037537178</v>
       </c>
       <c r="P5" t="n">
-        <v>383.7559593794721</v>
+        <v>383.7700242232699</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12768,28 +12805,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09540396019855711</v>
+        <v>0.0943851550347078</v>
       </c>
       <c r="J6" t="n">
+        <v>315</v>
+      </c>
+      <c r="K6" t="n">
         <v>314</v>
       </c>
-      <c r="K6" t="n">
-        <v>313</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03838916711343388</v>
+        <v>0.03781372021116858</v>
       </c>
       <c r="M6" t="n">
-        <v>2.80671124566479</v>
+        <v>2.803005607960787</v>
       </c>
       <c r="N6" t="n">
-        <v>12.27988634405637</v>
+        <v>12.24941146688185</v>
       </c>
       <c r="O6" t="n">
-        <v>3.504266876831212</v>
+        <v>3.499915922830412</v>
       </c>
       <c r="P6" t="n">
-        <v>382.5716937062276</v>
+        <v>382.5832264672845</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12827,7 +12864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G315"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24481,6 +24518,43 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-35.71412263086155,174.53156951696533</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-35.714558398122804,174.53230479410823</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>-35.71483653065417,174.533124830341</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-35.715075049029004,174.53395276411547</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-35.71526029722901,174.53480610813537</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
